--- a/評価シート改訂案/改訂案A_SABCD評価版.xlsx
+++ b/評価シート改訂案/改訂案A_SABCD評価版.xlsx
@@ -141,7 +141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -163,11 +163,128 @@
         <color rgb="00A6A6A6"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -251,6 +368,15 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -630,7 +756,7 @@
           <t>評価シート改訂案 A【SABCD評価版】　― 改訂のポイント ―</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
+      <c r="C2" s="29" t="n"/>
     </row>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
@@ -638,7 +764,7 @@
           <t>■ 現行シートの問題と、この案での対応</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
+      <c r="C4" s="29" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
@@ -660,7 +786,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>全項目に「期待水準（A）の定義」と着眼点を明記。S・B以下を付ける場合は「根拠となる事実」の記入を必須にした</t>
+          <t>全項目に「期待水準（A）の定義」と着眼点を明記。Aを含むすべての評価に「根拠となる事実」の記入を必須にした（書けない項目はB）</t>
         </is>
       </c>
     </row>
@@ -730,7 +856,7 @@
           <t>■ この案の仕組み</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
+      <c r="C13" s="29" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="B14" s="5" t="inlineStr">
@@ -738,7 +864,7 @@
           <t>・点数を廃止し、全項目をS・A・B・C・Dの5段階で評価する（プルダウンで選ぶだけ）</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
+      <c r="C14" s="29" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="B15" s="5" t="inlineStr">
@@ -746,71 +872,71 @@
           <t>・評価項目は3部署共通で10項目（成果3＋能力4＋姿勢3）。部署で変わるのは「成果」の中身だけ</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
+      <c r="C15" s="29" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>・総合評価は自動計算（成果50％・能力30％・姿勢20％の重み付け）で目安を出し、最終評価は評価者が決定。目安から変える場合は理由を記入する</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n"/>
-    </row>
-    <row r="17" ht="32" customHeight="1">
+          <t>・総合評価はExcelが自動計算（成果50％・能力30％・姿勢20％の重み付け）。総合Aは75点以上とし、成果の数字が伴わないと届かない基準にしている</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>・処遇への接続は現行どおり（S:+5号／A:+3号／B:±0／C:-1号／D:-3号）なので、給与制度はそのまま使える</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
+          <t>・最終評価と昇給幅は、これまでどおり社長が決定する（処遇の目安は現行どおり S:+5号／A:+3号／B:±0／C:-1号／D:-3号）</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>・S・B・C・Dには「根拠となる事実」の記入が必須。事実が書けない評価は付けられない仕組みで、感情の入り込みを防ぐ</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n"/>
+          <t>・Aを含むすべての評価に「根拠となる事実」の記入が必須。書けない項目はBになるため、「とりあえずA」や感情による評価を防げる</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>■ 運用ルール（シートよりも大事な4つ）</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n"/>
+          <t>■ 運用ルール</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>① A（期待どおり）が標準。全項目Aは「問題なくできている良い評価」であることを全員に説明する</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n"/>
+          <t>① A（期待どおり）が標準。ただし「何もしなくてもA」ではなく、「期待どおりやった事実がある」ことが条件</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>② S・B・C・Dを付けるときは「根拠となる事実」を必ず記入する（書けない場合はAに戻す）</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n"/>
-    </row>
-    <row r="23" ht="30" customHeight="1">
+          <t>② すべての項目に「根拠となる事実」を1行記入する（月報から転記でOK）。事実が書けない項目はB</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>③ 評価者同士で「目線合わせ会議」を評価前に30分行う（同じ事実に同じ評価が付くように）</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n"/>
+          <t>③ 総合評価はExcelが自動判定する。全項目Aなら80点で総合A、成果がB（数字未達）だと他がすべてAでも70点で総合B</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>④ 評価は必ず本人へのフィードバック面談（10〜15分）で説明する。月次ログがあれば話す材料に困らない</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n"/>
+          <t>④ 最終評価と昇給幅は、これまでどおり社長が決定する</t>
+        </is>
+      </c>
+      <c r="C24" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -855,8 +981,8 @@
           <t>評価基準の定義（SABCD）</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="29" t="n"/>
     </row>
     <row r="4">
       <c r="B4" s="6" t="inlineStr">
@@ -892,7 +1018,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>A</t>
@@ -900,7 +1026,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>期待水準を満たしている。＝「しっかりできている」状態。Aが標準であり、良い評価です</t>
+          <t>期待水準を満たしている（＝しっかりできている）。Aが標準であり、良い評価です。※期待どおりやった事実の記入が必須（書けない項目はB）</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -966,8 +1092,8 @@
           <t>■ 「なぜ満点じゃないのか？」への会社の答え方</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="29" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
@@ -975,8 +1101,8 @@
           <t>・この制度に「満点」はありません。A（期待どおり）が標準であり、良い評価です。</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="30" t="n"/>
+      <c r="D12" s="29" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="B13" s="5" t="inlineStr">
@@ -984,17 +1110,17 @@
           <t>・Sは「期待を超えた具体的な事実」を挙げられる場合にだけ付きます。逆に、Sを付けた評価者は事実を説明できなければなりません。</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-    </row>
-    <row r="14" ht="26" customHeight="1">
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="29" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>・B以下を付ける場合も同じく事実の記入が必須です。「なんとなく」では上げることも下げることもできません。</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
+          <t>・Aを含め、すべての項目に事実の記入が必須です。事実が書けない項目はBになるため、「なんとなく」で下げることも、甘くAを付けることもできません。</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="n"/>
+      <c r="D14" s="29" t="n"/>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="B15" s="5" t="inlineStr">
@@ -1002,8 +1128,8 @@
           <t>・つまり本人への説明は常に『基準はこれ、事実はこれ、だから評価はこれ』の3点セットで行えます。</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="29" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
@@ -1011,8 +1137,8 @@
           <t>■ 総合評価の決まり方</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="30" t="n"/>
+      <c r="D17" s="29" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
@@ -1020,26 +1146,27 @@
           <t>・各項目の評価をS=5〜D=1に換算し、成果50％・能力30％・姿勢20％の重みで100点換算した目安を自動計算します。</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-    </row>
-    <row r="19" ht="26" customHeight="1">
+      <c r="C18" s="30" t="n"/>
+      <c r="D18" s="29" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>・目安の換算：90点以上=S／70〜89=A／50〜69=B／40〜49=C／39以下=D</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
+          <t>・目安の換算：90点以上=S／75〜89=A／50〜74=B／40〜49=C／39以下=D
+　（全項目Aなら80点で総合A。成果がB＝数字未達だと、他がすべてAでも70点で総合B）</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="n"/>
+      <c r="D19" s="29" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>・最終評価は評価者が決定します。自動の目安から変える場合は、理由の記入が必須です（勤務態度・特別な事情など）。</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
+          <t>・最終評価と昇給幅は、これまでどおり社長が決定します。自動の目安から変える場合は、理由を記入します。</t>
+        </is>
+      </c>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -1087,13 +1214,13 @@
           <t>人事評価シート【SABCD評価版】　電算・編集</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
+      <c r="B1" s="30" t="n"/>
+      <c r="C1" s="30" t="n"/>
+      <c r="D1" s="30" t="n"/>
+      <c r="E1" s="30" t="n"/>
+      <c r="F1" s="30" t="n"/>
+      <c r="G1" s="30" t="n"/>
+      <c r="H1" s="29" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -1106,7 +1233,7 @@
           <t>氏名</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
+      <c r="C3" s="29" t="n"/>
       <c r="D3" s="13" t="inlineStr">
         <is>
           <t>評価期間</t>
@@ -1136,7 +1263,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="14" t="inlineStr"/>
       <c r="B4" s="14" t="inlineStr"/>
-      <c r="C4" s="2" t="n"/>
+      <c r="C4" s="29" t="n"/>
       <c r="D4" s="14" t="inlineStr"/>
       <c r="E4" s="14" t="inlineStr"/>
       <c r="F4" s="14" t="inlineStr"/>
@@ -1150,30 +1277,30 @@
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="29" t="n"/>
       <c r="E5" s="13" t="inlineStr">
         <is>
           <t>個人目標</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="G5" s="30" t="n"/>
+      <c r="H5" s="29" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>使い方：各項目をS〜Dのプルダウンで選ぶ（A＝期待どおり＝標準の良い評価）。S・B・C・Dを付けた項目は「根拠となる事実」を必ず記入（「日々の記録」シートから転記でOK）。基準は「評価基準の定義」シート参照。</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+          <t>使い方：各項目をS〜Dのプルダウンで選ぶ（A＝期待どおり＝標準の良い評価）。すべての項目に「根拠となる事実」を1行記入（「日々の記録」シートから転記でOK）。事実が書けない項目はB。基準は「評価基準の定義」シート参照。</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="n"/>
+      <c r="C6" s="30" t="n"/>
+      <c r="D6" s="30" t="n"/>
+      <c r="E6" s="30" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
+      <c r="H6" s="29" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1251,7 +1378,7 @@
       </c>
     </row>
     <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="2" t="n"/>
+      <c r="A10" s="31" t="n"/>
       <c r="B10" s="8" t="n">
         <v>2</v>
       </c>
@@ -1280,7 +1407,7 @@
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="2" t="n"/>
+      <c r="A11" s="32" t="n"/>
       <c r="B11" s="8" t="n">
         <v>3</v>
       </c>
@@ -1342,7 +1469,7 @@
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="2" t="n"/>
+      <c r="A13" s="31" t="n"/>
       <c r="B13" s="8" t="n">
         <v>5</v>
       </c>
@@ -1371,7 +1498,7 @@
       </c>
     </row>
     <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="2" t="n"/>
+      <c r="A14" s="31" t="n"/>
       <c r="B14" s="8" t="n">
         <v>6</v>
       </c>
@@ -1400,7 +1527,7 @@
       </c>
     </row>
     <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="2" t="n"/>
+      <c r="A15" s="32" t="n"/>
       <c r="B15" s="8" t="n">
         <v>7</v>
       </c>
@@ -1462,7 +1589,7 @@
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="2" t="n"/>
+      <c r="A17" s="31" t="n"/>
       <c r="B17" s="8" t="n">
         <v>9</v>
       </c>
@@ -1491,7 +1618,7 @@
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="2" t="n"/>
+      <c r="A18" s="32" t="n"/>
       <c r="B18" s="8" t="n">
         <v>10</v>
       </c>
@@ -1525,13 +1652,13 @@
           <t>総合評価</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="B20" s="30" t="n"/>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="30" t="n"/>
+      <c r="E20" s="30" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+      <c r="H20" s="29" t="n"/>
     </row>
     <row r="21">
       <c r="C21" s="13" t="inlineStr">
@@ -1539,7 +1666,7 @@
           <t>区分</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="D21" s="29" t="n"/>
       <c r="E21" s="13" t="inlineStr">
         <is>
           <t>自己</t>
@@ -1555,7 +1682,7 @@
           <t>重み：成果50％・能力30％・姿勢20％（詳細は「評価基準の定義」）</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n"/>
+      <c r="H21" s="29" t="n"/>
     </row>
     <row r="22">
       <c r="C22" s="25" t="inlineStr">
@@ -1563,7 +1690,7 @@
           <t>換算点（100点換算・自動）</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="D22" s="29" t="n"/>
       <c r="E22" s="8">
         <f>IFERROR(ROUND(AVERAGE(I9:I11)/5*50+AVERAGE(I12:I15)/5*30+AVERAGE(I16:I18)/5*20,1),"")</f>
         <v/>
@@ -1579,27 +1706,27 @@
           <t>総合評価（自動・目安）</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="D23" s="29" t="n"/>
       <c r="E23" s="26">
-        <f>IF(E22="","",IF(E22&gt;=90,"S",IF(E22&gt;=70,"A",IF(E22&gt;=50,"B",IF(E22&gt;=40,"C","D")))))</f>
+        <f>IF(E22="","",IF(E22&gt;=90,"S",IF(E22&gt;=75,"A",IF(E22&gt;=50,"B",IF(E22&gt;=40,"C","D")))))</f>
         <v/>
       </c>
       <c r="F23" s="26">
-        <f>IF(F22="","",IF(F22&gt;=90,"S",IF(F22&gt;=70,"A",IF(F22&gt;=50,"B",IF(F22&gt;=40,"C","D")))))</f>
+        <f>IF(F22="","",IF(F22&gt;=90,"S",IF(F22&gt;=75,"A",IF(F22&gt;=50,"B",IF(F22&gt;=40,"C","D")))))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="C24" s="25" t="inlineStr">
         <is>
-          <t>最終総合評価（評価者が決定）※自動の目安から変更する場合は右の欄に理由を記入</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n"/>
+          <t>最終総合評価（社長が決定）※自動の目安から変更する場合は右の欄に理由を記入</t>
+        </is>
+      </c>
+      <c r="D24" s="29" t="n"/>
       <c r="E24" s="16" t="inlineStr"/>
       <c r="F24" s="27" t="inlineStr"/>
       <c r="G24" s="15" t="inlineStr"/>
-      <c r="H24" s="2" t="n"/>
+      <c r="H24" s="29" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="28" t="inlineStr">
@@ -1607,33 +1734,33 @@
           <t>本人コメント（今期の振り返り：「日々の記録」シートから転記でOK）</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
+      <c r="B26" s="30" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="30" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+      <c r="H26" s="29" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="20" t="inlineStr"/>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
+      <c r="B27" s="33" t="n"/>
+      <c r="C27" s="33" t="n"/>
+      <c r="D27" s="33" t="n"/>
+      <c r="E27" s="33" t="n"/>
+      <c r="F27" s="33" t="n"/>
+      <c r="G27" s="33" t="n"/>
+      <c r="H27" s="34" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="A28" s="35" t="n"/>
+      <c r="B28" s="36" t="n"/>
+      <c r="C28" s="36" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="36" t="n"/>
+      <c r="F28" s="36" t="n"/>
+      <c r="G28" s="36" t="n"/>
+      <c r="H28" s="37" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="28" t="inlineStr">
@@ -1641,33 +1768,33 @@
           <t>評価者コメント（総評：良かった点をひとつ＋来期に期待することをひとつ、必ず書く）</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
+      <c r="B29" s="30" t="n"/>
+      <c r="C29" s="30" t="n"/>
+      <c r="D29" s="30" t="n"/>
+      <c r="E29" s="30" t="n"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
+      <c r="H29" s="29" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="20" t="inlineStr"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
+      <c r="B30" s="33" t="n"/>
+      <c r="C30" s="33" t="n"/>
+      <c r="D30" s="33" t="n"/>
+      <c r="E30" s="33" t="n"/>
+      <c r="F30" s="33" t="n"/>
+      <c r="G30" s="33" t="n"/>
+      <c r="H30" s="34" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
+      <c r="A31" s="35" t="n"/>
+      <c r="B31" s="36" t="n"/>
+      <c r="C31" s="36" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="36" t="n"/>
+      <c r="G31" s="36" t="n"/>
+      <c r="H31" s="37" t="n"/>
     </row>
     <row r="32">
       <c r="C32" s="13" t="inlineStr">
@@ -1692,8 +1819,8 @@
   </sheetData>
   <mergeCells count="21">
     <mergeCell ref="G21:H21"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="F5:H5"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A6:H6"/>
@@ -1751,13 +1878,13 @@
           <t>人事評価シート【SABCD評価版】　営業</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
+      <c r="B1" s="30" t="n"/>
+      <c r="C1" s="30" t="n"/>
+      <c r="D1" s="30" t="n"/>
+      <c r="E1" s="30" t="n"/>
+      <c r="F1" s="30" t="n"/>
+      <c r="G1" s="30" t="n"/>
+      <c r="H1" s="29" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -1770,7 +1897,7 @@
           <t>氏名</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
+      <c r="C3" s="29" t="n"/>
       <c r="D3" s="13" t="inlineStr">
         <is>
           <t>評価期間</t>
@@ -1800,7 +1927,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="14" t="inlineStr"/>
       <c r="B4" s="14" t="inlineStr"/>
-      <c r="C4" s="2" t="n"/>
+      <c r="C4" s="29" t="n"/>
       <c r="D4" s="14" t="inlineStr"/>
       <c r="E4" s="14" t="inlineStr"/>
       <c r="F4" s="14" t="inlineStr"/>
@@ -1814,30 +1941,30 @@
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="29" t="n"/>
       <c r="E5" s="13" t="inlineStr">
         <is>
           <t>個人目標</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="G5" s="30" t="n"/>
+      <c r="H5" s="29" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>使い方：各項目をS〜Dのプルダウンで選ぶ（A＝期待どおり＝標準の良い評価）。S・B・C・Dを付けた項目は「根拠となる事実」を必ず記入（「日々の記録」シートから転記でOK）。基準は「評価基準の定義」シート参照。</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+          <t>使い方：各項目をS〜Dのプルダウンで選ぶ（A＝期待どおり＝標準の良い評価）。すべての項目に「根拠となる事実」を1行記入（「日々の記録」シートから転記でOK）。事実が書けない項目はB。基準は「評価基準の定義」シート参照。</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="n"/>
+      <c r="C6" s="30" t="n"/>
+      <c r="D6" s="30" t="n"/>
+      <c r="E6" s="30" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
+      <c r="H6" s="29" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1915,7 +2042,7 @@
       </c>
     </row>
     <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="2" t="n"/>
+      <c r="A10" s="31" t="n"/>
       <c r="B10" s="8" t="n">
         <v>2</v>
       </c>
@@ -1944,7 +2071,7 @@
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="2" t="n"/>
+      <c r="A11" s="32" t="n"/>
       <c r="B11" s="8" t="n">
         <v>3</v>
       </c>
@@ -2006,7 +2133,7 @@
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="2" t="n"/>
+      <c r="A13" s="31" t="n"/>
       <c r="B13" s="8" t="n">
         <v>5</v>
       </c>
@@ -2035,7 +2162,7 @@
       </c>
     </row>
     <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="2" t="n"/>
+      <c r="A14" s="31" t="n"/>
       <c r="B14" s="8" t="n">
         <v>6</v>
       </c>
@@ -2064,7 +2191,7 @@
       </c>
     </row>
     <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="2" t="n"/>
+      <c r="A15" s="32" t="n"/>
       <c r="B15" s="8" t="n">
         <v>7</v>
       </c>
@@ -2126,7 +2253,7 @@
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="2" t="n"/>
+      <c r="A17" s="31" t="n"/>
       <c r="B17" s="8" t="n">
         <v>9</v>
       </c>
@@ -2155,7 +2282,7 @@
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="2" t="n"/>
+      <c r="A18" s="32" t="n"/>
       <c r="B18" s="8" t="n">
         <v>10</v>
       </c>
@@ -2189,13 +2316,13 @@
           <t>総合評価</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="B20" s="30" t="n"/>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="30" t="n"/>
+      <c r="E20" s="30" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+      <c r="H20" s="29" t="n"/>
     </row>
     <row r="21">
       <c r="C21" s="13" t="inlineStr">
@@ -2203,7 +2330,7 @@
           <t>区分</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="D21" s="29" t="n"/>
       <c r="E21" s="13" t="inlineStr">
         <is>
           <t>自己</t>
@@ -2219,7 +2346,7 @@
           <t>重み：成果50％・能力30％・姿勢20％（詳細は「評価基準の定義」）</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n"/>
+      <c r="H21" s="29" t="n"/>
     </row>
     <row r="22">
       <c r="C22" s="25" t="inlineStr">
@@ -2227,7 +2354,7 @@
           <t>換算点（100点換算・自動）</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="D22" s="29" t="n"/>
       <c r="E22" s="8">
         <f>IFERROR(ROUND(AVERAGE(I9:I11)/5*50+AVERAGE(I12:I15)/5*30+AVERAGE(I16:I18)/5*20,1),"")</f>
         <v/>
@@ -2243,27 +2370,27 @@
           <t>総合評価（自動・目安）</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="D23" s="29" t="n"/>
       <c r="E23" s="26">
-        <f>IF(E22="","",IF(E22&gt;=90,"S",IF(E22&gt;=70,"A",IF(E22&gt;=50,"B",IF(E22&gt;=40,"C","D")))))</f>
+        <f>IF(E22="","",IF(E22&gt;=90,"S",IF(E22&gt;=75,"A",IF(E22&gt;=50,"B",IF(E22&gt;=40,"C","D")))))</f>
         <v/>
       </c>
       <c r="F23" s="26">
-        <f>IF(F22="","",IF(F22&gt;=90,"S",IF(F22&gt;=70,"A",IF(F22&gt;=50,"B",IF(F22&gt;=40,"C","D")))))</f>
+        <f>IF(F22="","",IF(F22&gt;=90,"S",IF(F22&gt;=75,"A",IF(F22&gt;=50,"B",IF(F22&gt;=40,"C","D")))))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="C24" s="25" t="inlineStr">
         <is>
-          <t>最終総合評価（評価者が決定）※自動の目安から変更する場合は右の欄に理由を記入</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n"/>
+          <t>最終総合評価（社長が決定）※自動の目安から変更する場合は右の欄に理由を記入</t>
+        </is>
+      </c>
+      <c r="D24" s="29" t="n"/>
       <c r="E24" s="16" t="inlineStr"/>
       <c r="F24" s="27" t="inlineStr"/>
       <c r="G24" s="15" t="inlineStr"/>
-      <c r="H24" s="2" t="n"/>
+      <c r="H24" s="29" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="28" t="inlineStr">
@@ -2271,33 +2398,33 @@
           <t>本人コメント（今期の振り返り：「日々の記録」シートから転記でOK）</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
+      <c r="B26" s="30" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="30" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+      <c r="H26" s="29" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="20" t="inlineStr"/>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
+      <c r="B27" s="33" t="n"/>
+      <c r="C27" s="33" t="n"/>
+      <c r="D27" s="33" t="n"/>
+      <c r="E27" s="33" t="n"/>
+      <c r="F27" s="33" t="n"/>
+      <c r="G27" s="33" t="n"/>
+      <c r="H27" s="34" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="A28" s="35" t="n"/>
+      <c r="B28" s="36" t="n"/>
+      <c r="C28" s="36" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="36" t="n"/>
+      <c r="F28" s="36" t="n"/>
+      <c r="G28" s="36" t="n"/>
+      <c r="H28" s="37" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="28" t="inlineStr">
@@ -2305,33 +2432,33 @@
           <t>評価者コメント（総評：良かった点をひとつ＋来期に期待することをひとつ、必ず書く）</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
+      <c r="B29" s="30" t="n"/>
+      <c r="C29" s="30" t="n"/>
+      <c r="D29" s="30" t="n"/>
+      <c r="E29" s="30" t="n"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
+      <c r="H29" s="29" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="20" t="inlineStr"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
+      <c r="B30" s="33" t="n"/>
+      <c r="C30" s="33" t="n"/>
+      <c r="D30" s="33" t="n"/>
+      <c r="E30" s="33" t="n"/>
+      <c r="F30" s="33" t="n"/>
+      <c r="G30" s="33" t="n"/>
+      <c r="H30" s="34" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
+      <c r="A31" s="35" t="n"/>
+      <c r="B31" s="36" t="n"/>
+      <c r="C31" s="36" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="36" t="n"/>
+      <c r="G31" s="36" t="n"/>
+      <c r="H31" s="37" t="n"/>
     </row>
     <row r="32">
       <c r="C32" s="13" t="inlineStr">
@@ -2356,8 +2483,8 @@
   </sheetData>
   <mergeCells count="21">
     <mergeCell ref="G21:H21"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="F5:H5"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A6:H6"/>
@@ -2415,13 +2542,13 @@
           <t>人事評価シート【SABCD評価版】　工場</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
+      <c r="B1" s="30" t="n"/>
+      <c r="C1" s="30" t="n"/>
+      <c r="D1" s="30" t="n"/>
+      <c r="E1" s="30" t="n"/>
+      <c r="F1" s="30" t="n"/>
+      <c r="G1" s="30" t="n"/>
+      <c r="H1" s="29" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -2434,7 +2561,7 @@
           <t>氏名</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
+      <c r="C3" s="29" t="n"/>
       <c r="D3" s="13" t="inlineStr">
         <is>
           <t>評価期間</t>
@@ -2464,7 +2591,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="14" t="inlineStr"/>
       <c r="B4" s="14" t="inlineStr"/>
-      <c r="C4" s="2" t="n"/>
+      <c r="C4" s="29" t="n"/>
       <c r="D4" s="14" t="inlineStr"/>
       <c r="E4" s="14" t="inlineStr"/>
       <c r="F4" s="14" t="inlineStr"/>
@@ -2478,30 +2605,30 @@
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="29" t="n"/>
       <c r="E5" s="13" t="inlineStr">
         <is>
           <t>個人目標</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="G5" s="30" t="n"/>
+      <c r="H5" s="29" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>使い方：各項目をS〜Dのプルダウンで選ぶ（A＝期待どおり＝標準の良い評価）。S・B・C・Dを付けた項目は「根拠となる事実」を必ず記入（「日々の記録」シートから転記でOK）。基準は「評価基準の定義」シート参照。</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+          <t>使い方：各項目をS〜Dのプルダウンで選ぶ（A＝期待どおり＝標準の良い評価）。すべての項目に「根拠となる事実」を1行記入（「日々の記録」シートから転記でOK）。事実が書けない項目はB。基準は「評価基準の定義」シート参照。</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="n"/>
+      <c r="C6" s="30" t="n"/>
+      <c r="D6" s="30" t="n"/>
+      <c r="E6" s="30" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
+      <c r="H6" s="29" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2579,7 +2706,7 @@
       </c>
     </row>
     <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="2" t="n"/>
+      <c r="A10" s="31" t="n"/>
       <c r="B10" s="8" t="n">
         <v>2</v>
       </c>
@@ -2608,7 +2735,7 @@
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="2" t="n"/>
+      <c r="A11" s="32" t="n"/>
       <c r="B11" s="8" t="n">
         <v>3</v>
       </c>
@@ -2670,7 +2797,7 @@
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="2" t="n"/>
+      <c r="A13" s="31" t="n"/>
       <c r="B13" s="8" t="n">
         <v>5</v>
       </c>
@@ -2699,7 +2826,7 @@
       </c>
     </row>
     <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="2" t="n"/>
+      <c r="A14" s="31" t="n"/>
       <c r="B14" s="8" t="n">
         <v>6</v>
       </c>
@@ -2728,7 +2855,7 @@
       </c>
     </row>
     <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="2" t="n"/>
+      <c r="A15" s="32" t="n"/>
       <c r="B15" s="8" t="n">
         <v>7</v>
       </c>
@@ -2790,7 +2917,7 @@
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="2" t="n"/>
+      <c r="A17" s="31" t="n"/>
       <c r="B17" s="8" t="n">
         <v>9</v>
       </c>
@@ -2819,7 +2946,7 @@
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="2" t="n"/>
+      <c r="A18" s="32" t="n"/>
       <c r="B18" s="8" t="n">
         <v>10</v>
       </c>
@@ -2853,13 +2980,13 @@
           <t>総合評価</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="B20" s="30" t="n"/>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="30" t="n"/>
+      <c r="E20" s="30" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+      <c r="H20" s="29" t="n"/>
     </row>
     <row r="21">
       <c r="C21" s="13" t="inlineStr">
@@ -2867,7 +2994,7 @@
           <t>区分</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="D21" s="29" t="n"/>
       <c r="E21" s="13" t="inlineStr">
         <is>
           <t>自己</t>
@@ -2883,7 +3010,7 @@
           <t>重み：成果50％・能力30％・姿勢20％（詳細は「評価基準の定義」）</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n"/>
+      <c r="H21" s="29" t="n"/>
     </row>
     <row r="22">
       <c r="C22" s="25" t="inlineStr">
@@ -2891,7 +3018,7 @@
           <t>換算点（100点換算・自動）</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="D22" s="29" t="n"/>
       <c r="E22" s="8">
         <f>IFERROR(ROUND(AVERAGE(I9:I11)/5*50+AVERAGE(I12:I15)/5*30+AVERAGE(I16:I18)/5*20,1),"")</f>
         <v/>
@@ -2907,27 +3034,27 @@
           <t>総合評価（自動・目安）</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="D23" s="29" t="n"/>
       <c r="E23" s="26">
-        <f>IF(E22="","",IF(E22&gt;=90,"S",IF(E22&gt;=70,"A",IF(E22&gt;=50,"B",IF(E22&gt;=40,"C","D")))))</f>
+        <f>IF(E22="","",IF(E22&gt;=90,"S",IF(E22&gt;=75,"A",IF(E22&gt;=50,"B",IF(E22&gt;=40,"C","D")))))</f>
         <v/>
       </c>
       <c r="F23" s="26">
-        <f>IF(F22="","",IF(F22&gt;=90,"S",IF(F22&gt;=70,"A",IF(F22&gt;=50,"B",IF(F22&gt;=40,"C","D")))))</f>
+        <f>IF(F22="","",IF(F22&gt;=90,"S",IF(F22&gt;=75,"A",IF(F22&gt;=50,"B",IF(F22&gt;=40,"C","D")))))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="C24" s="25" t="inlineStr">
         <is>
-          <t>最終総合評価（評価者が決定）※自動の目安から変更する場合は右の欄に理由を記入</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n"/>
+          <t>最終総合評価（社長が決定）※自動の目安から変更する場合は右の欄に理由を記入</t>
+        </is>
+      </c>
+      <c r="D24" s="29" t="n"/>
       <c r="E24" s="16" t="inlineStr"/>
       <c r="F24" s="27" t="inlineStr"/>
       <c r="G24" s="15" t="inlineStr"/>
-      <c r="H24" s="2" t="n"/>
+      <c r="H24" s="29" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="28" t="inlineStr">
@@ -2935,33 +3062,33 @@
           <t>本人コメント（今期の振り返り：「日々の記録」シートから転記でOK）</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
+      <c r="B26" s="30" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="30" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+      <c r="H26" s="29" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="20" t="inlineStr"/>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
+      <c r="B27" s="33" t="n"/>
+      <c r="C27" s="33" t="n"/>
+      <c r="D27" s="33" t="n"/>
+      <c r="E27" s="33" t="n"/>
+      <c r="F27" s="33" t="n"/>
+      <c r="G27" s="33" t="n"/>
+      <c r="H27" s="34" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="A28" s="35" t="n"/>
+      <c r="B28" s="36" t="n"/>
+      <c r="C28" s="36" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="36" t="n"/>
+      <c r="F28" s="36" t="n"/>
+      <c r="G28" s="36" t="n"/>
+      <c r="H28" s="37" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="28" t="inlineStr">
@@ -2969,33 +3096,33 @@
           <t>評価者コメント（総評：良かった点をひとつ＋来期に期待することをひとつ、必ず書く）</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
+      <c r="B29" s="30" t="n"/>
+      <c r="C29" s="30" t="n"/>
+      <c r="D29" s="30" t="n"/>
+      <c r="E29" s="30" t="n"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
+      <c r="H29" s="29" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="20" t="inlineStr"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
+      <c r="B30" s="33" t="n"/>
+      <c r="C30" s="33" t="n"/>
+      <c r="D30" s="33" t="n"/>
+      <c r="E30" s="33" t="n"/>
+      <c r="F30" s="33" t="n"/>
+      <c r="G30" s="33" t="n"/>
+      <c r="H30" s="34" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
+      <c r="A31" s="35" t="n"/>
+      <c r="B31" s="36" t="n"/>
+      <c r="C31" s="36" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="36" t="n"/>
+      <c r="G31" s="36" t="n"/>
+      <c r="H31" s="37" t="n"/>
     </row>
     <row r="32">
       <c r="C32" s="13" t="inlineStr">
@@ -3020,8 +3147,8 @@
   </sheetData>
   <mergeCells count="21">
     <mergeCell ref="G21:H21"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="F5:H5"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A6:H6"/>
@@ -3074,9 +3201,9 @@
           <t>日々の記録（月次ログ）　― 月末に5分、1行ずつでOK ―</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="30" t="n"/>
+      <c r="E2" s="29" t="n"/>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="B3" s="16" t="inlineStr">
@@ -3084,9 +3211,9 @@
           <t>使い方：月末に「良かったこと・成果」「課題・反省」を1行ずつ書くだけ。上司も気づいたことがあれば一言。期末の評価シートの「根拠となる事実」「本人コメント」は、ここから転記すれば書けます（記憶に頼らない・直近だけで評価しないための仕組み）。</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
+      <c r="C3" s="30" t="n"/>
+      <c r="D3" s="30" t="n"/>
+      <c r="E3" s="29" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="6" t="inlineStr">
